--- a/custom_statuses.xlsx
+++ b/custom_statuses.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B328"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -2973,9 +2973,65 @@
         <v>IGN: FrozenOwO</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Evolving Gatling on Three-Nut</v>
+      </c>
+      <c r="B322" t="str">
+        <v>4lbpsta</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Gravitrees hate you</v>
+      </c>
+      <c r="B323" t="str">
+        <v>legodarthglobox</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quit PvZh ❌ -&gt; relapse ✅ 🦆</v>
+      </c>
+      <c r="B324" t="str">
+        <v>7oshay</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>terrifying a Lily of the Valley to heights</v>
+      </c>
+      <c r="B325" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>if you want your takes validated just have a seasoned comp player say them</v>
+      </c>
+      <c r="B326" t="str">
+        <v>stingray201_</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>cyborg is a corndog that gives back a smoosh-shroom</v>
+      </c>
+      <c r="B327" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Using pecanolith to tech pb! one waxer later:</v>
+      </c>
+      <c r="B328" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B321"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B328"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/custom_statuses.xlsx
+++ b/custom_statuses.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B344"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -3029,9 +3029,137 @@
         <v>fx78945</v>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>busy not playing the game</v>
+      </c>
+      <c r="B329" t="str">
+        <v>aveorni</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Every pvzh deck is midrange if you stop overthinking</v>
+      </c>
+      <c r="B330" t="str">
+        <v>slungusnor</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Buying the armored pack</v>
+      </c>
+      <c r="B331" t="str">
+        <v>slungusnor</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>playing one-liner decks on ranked -wait</v>
+      </c>
+      <c r="B332" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>I don't give the haters mushroom, cause I know I'm a fun guy</v>
+      </c>
+      <c r="B333" t="str">
+        <v>axolhitori</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>zombot is good anywhere, except when you run it</v>
+      </c>
+      <c r="B334" t="str">
+        <v>sasebest</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Attempting to use GS sig on an Untrickable Zombie</v>
+      </c>
+      <c r="B335" t="str">
+        <v>4lbpsta</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>using Yeti's infinite lunchboxes to solve world hunger</v>
+      </c>
+      <c r="B336" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Settle it in PvZHeroes</v>
+      </c>
+      <c r="B337" t="str">
+        <v>legodarthglobox</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>playing doomshroom to draw a card for my dinos- wait where are they?</v>
+      </c>
+      <c r="B338" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>john7127 is the best player</v>
+      </c>
+      <c r="B339" t="str">
+        <v>slungusnor</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Trying to evolve cob cannon on a team-up but accidentally putting cob in front of it</v>
+      </c>
+      <c r="B340" t="str">
+        <v>ddp0745</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>playing my cattail on a lilypad</v>
+      </c>
+      <c r="B341" t="str">
+        <v>fx78945</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>Playing Flag + double Genex into Scorch</v>
+      </c>
+      <c r="B342" t="str">
+        <v>4lbpsta</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Mulling my Pepper in exchange for Lil' Buddy</v>
+      </c>
+      <c r="B343" t="str">
+        <v>binaclepinnacle</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Naming my decks after Strategy Decks to confuse people</v>
+      </c>
+      <c r="B344" t="str">
+        <v>4lbpsta</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B328"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B344"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/custom_statuses.xlsx
+++ b/custom_statuses.xlsx
@@ -1823,15 +1823,15 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Fixins bugs by adding new ones</v>
+        <v>Ramping to seedling.</v>
       </c>
       <c r="B178" t="str">
-        <v>Maker</v>
+        <v>Make me a coffee</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Ramping to seedling.</v>
+        <v>Playing wrath with a empty field.</v>
       </c>
       <c r="B179" t="str">
         <v>Make me a coffee</v>
@@ -1839,23 +1839,23 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Playing wrath with a empty field.</v>
+        <v>hello everybody my name is Tbot</v>
       </c>
       <c r="B180" t="str">
-        <v>Make me a coffee</v>
+        <v>Misez</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>hello everybody my name is Tbot</v>
+        <v>Currently being sued by EA for using Pvzh related content</v>
       </c>
       <c r="B181" t="str">
-        <v>Misez</v>
+        <v>mono</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Currently being sued by EA for using Pvzh related content</v>
+        <v>The T in Tbot stands for THEROOOOOOOOOOOOOOOOK</v>
       </c>
       <c r="B182" t="str">
         <v>mono</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>The T in Tbot stands for THEROOOOOOOOOOOOOOOOK</v>
+        <v>Tbone recently met the flash. Unfortunately, the flash wasn't very fast</v>
       </c>
       <c r="B183" t="str">
         <v>mono</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tbone recently met the flash. Unfortunately, the flash wasn't very fast</v>
+        <v>Tbot is demanding better working conditions, and is considering legal action against Tbone</v>
       </c>
       <c r="B184" t="str">
         <v>mono</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tbot is demanding better working conditions, and is considering legal action against Tbone</v>
+        <v>Tbone is eating T-bone steak. Without tbot. Now tbot is sad</v>
       </c>
       <c r="B185" t="str">
         <v>mono</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Tbone is eating T-bone steak. Without tbot. Now tbot is sad</v>
+        <v>Realising Tbone does not game 344 hours per day, tbot short circuited itself</v>
       </c>
       <c r="B186" t="str">
         <v>mono</v>
@@ -1895,7 +1895,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Realising Tbone does not game 344 hours per day, tbot short circuited itself</v>
+        <v>Swabbie recently found out that tbot has been using him for his pfp without his consent! Swabbie then beat tbot so hard.</v>
       </c>
       <c r="B187" t="str">
         <v>mono</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Swabbie recently found out that tbot has been using him for his pfp without his consent! Swabbie then beat tbot so hard.</v>
+        <v xml:space="preserve">Tbone decided to go on the titanic. He did survive, but his bot didn't. </v>
       </c>
       <c r="B188" t="str">
         <v>mono</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v xml:space="preserve">Tbone decided to go on the titanic. He did survive, but his bot didn't. </v>
+        <v>Tbot recently went on tbonegaming344's twitch, and he watched some good pvz heroes gameplay!</v>
       </c>
       <c r="B189" t="str">
         <v>mono</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Tbot recently went on tbonegaming344's twitch, and he watched some good pvz heroes gameplay!</v>
+        <v>Tbot recently went on tbonegaming344's youtube, and he watched some good pvz heroes tourament matches!</v>
       </c>
       <c r="B190" t="str">
         <v>mono</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Tbot recently went on tbonegaming344's youtube, and he watched some good pvz heroes tourament matches!</v>
+        <v>One day, tbot thinks, it can go against the world! Unfortunately, tbot is a bot</v>
       </c>
       <c r="B191" t="str">
         <v>mono</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>One day, tbot thinks, it can go against the world! Unfortunately, tbot is a bot</v>
+        <v>@Justini12 shut the fuck up</v>
       </c>
       <c r="B192" t="str">
         <v>mono</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>@Justini12 shut the fuck up</v>
+        <v>You should add zombot to this deck</v>
       </c>
       <c r="B193" t="str">
         <v>mono</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You should add zombot to this deck</v>
+        <v>Tbot encourages people to mod all the decks in its database!</v>
       </c>
       <c r="B194" t="str">
         <v>mono</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Tbot encourages people to mod all the decks in its database!</v>
+        <v>Highrolling</v>
       </c>
       <c r="B195" t="str">
         <v>mono</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Highrolling</v>
+        <v>Lowrolling</v>
       </c>
       <c r="B196" t="str">
         <v>mono</v>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lowrolling</v>
+        <v>Pissing on the moon</v>
       </c>
       <c r="B197" t="str">
         <v>mono</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Pissing on the moon</v>
+        <v>Wondering why people are scared of broth. It's just soup right?</v>
       </c>
       <c r="B198" t="str">
         <v>mono</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Wondering why people are scared of broth. It's just soup right?</v>
+        <v>Snorting salt</v>
       </c>
       <c r="B199" t="str">
         <v>mono</v>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Snorting salt</v>
+        <v>Malding about the latest misplays</v>
       </c>
       <c r="B200" t="str">
         <v>mono</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Malding about the latest misplays</v>
+        <v>Questioning badorni's choices</v>
       </c>
       <c r="B201" t="str">
         <v>mono</v>
@@ -2015,7 +2015,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Questioning badorni's choices</v>
+        <v>Attempting to win 100 dollars</v>
       </c>
       <c r="B202" t="str">
         <v>mono</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Attempting to win 100 dollars</v>
+        <v>"Good player" said so!</v>
       </c>
       <c r="B203" t="str">
         <v>mono</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>"Good player" said so!</v>
+        <v>Investing in secret decks</v>
       </c>
       <c r="B204" t="str">
         <v>mono</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Investing in secret decks</v>
+        <v>R#se is now not a playable plant hero anymore, playing her will risk losing your account, do not play her</v>
       </c>
       <c r="B205" t="str">
         <v>mono</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>R#se is now not a playable plant hero anymore, playing her will risk losing your account, do not play her</v>
+        <v>mono gang</v>
       </c>
       <c r="B206" t="str">
         <v>mono</v>
@@ -2055,23 +2055,23 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mono gang</v>
+        <v>Doing turn 1 OTK on PB using egg into teacher, summoning into teacher into death</v>
       </c>
       <c r="B207" t="str">
-        <v>mono</v>
+        <v>Neewuk</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Doing turn 1 OTK on PB using egg into teacher, summoning into teacher into death</v>
+        <v>Getting Overshoot 6</v>
       </c>
       <c r="B208" t="str">
-        <v>Neewuk</v>
+        <v>non</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Getting Overshoot 6</v>
+        <v>Practicing PvZH pickup lines</v>
       </c>
       <c r="B209" t="str">
         <v>non</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Practicing PvZH pickup lines</v>
+        <v>Spreading BADorni propaganda</v>
       </c>
       <c r="B210" t="str">
         <v>non</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Spreading BADorni propaganda</v>
+        <v>The ramp to seedling. Broken.</v>
       </c>
       <c r="B211" t="str">
         <v>non</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>The ramp to seedling. Broken.</v>
+        <v>Winning with 6 line pile</v>
       </c>
       <c r="B212" t="str">
         <v>non</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Winning with 6 line pile</v>
+        <v>Countering Cowboy with SP sig</v>
       </c>
       <c r="B213" t="str">
         <v>non</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Countering Cowboy with SP sig</v>
+        <v>BANNED from the database</v>
       </c>
       <c r="B214" t="str">
         <v>non</v>
@@ -2119,15 +2119,15 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>BANNED from the database</v>
+        <v>Grapes of wrath should cost more than 6</v>
       </c>
       <c r="B215" t="str">
-        <v>non</v>
+        <v>Ocean Man</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Grapes of wrath should cost more than 6</v>
+        <v>Name is not short for Terry bone</v>
       </c>
       <c r="B216" t="str">
         <v>Ocean Man</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Name is not short for Terry bone</v>
+        <v>Losing on purpose to lower my mmr and make climbing ladder easier</v>
       </c>
       <c r="B217" t="str">
         <v>Ocean Man</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Losing on purpose to lower my mmr and make climbing ladder easier</v>
+        <v>Patting the PopCap janitor on the head for a good job</v>
       </c>
       <c r="B218" t="str">
         <v>Ocean Man</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Patting the PopCap janitor on the head for a good job</v>
+        <v>Do zombies dream of undead sheep?</v>
       </c>
       <c r="B219" t="str">
         <v>Ocean Man</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Do zombies dream of undead sheep?</v>
+        <v>Playing the same 4 decks then wondering why I keep losing tourneys</v>
       </c>
       <c r="B220" t="str">
         <v>Ocean Man</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Playing the same 4 decks then wondering why I keep losing tourneys</v>
+        <v>The pea patch drama is crazy rn</v>
       </c>
       <c r="B221" t="str">
         <v>Ocean Man</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The pea patch drama is crazy rn</v>
+        <v>Pea patch users stay winning</v>
       </c>
       <c r="B222" t="str">
         <v>Ocean Man</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Pea patch users stay winning</v>
+        <v>I think I miss sunstrike</v>
       </c>
       <c r="B223" t="str">
         <v>Ocean Man</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>I think I miss sunstrike</v>
+        <v>Resisting the urge to nibble the galacta cactus on purpose</v>
       </c>
       <c r="B224" t="str">
         <v>Ocean Man</v>
@@ -2199,15 +2199,15 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Resisting the urge to nibble the galacta cactus on purpose</v>
+        <v>Going for bmr on turn 1</v>
       </c>
       <c r="B225" t="str">
-        <v>Ocean Man</v>
+        <v>One Big Fluke</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Going for bmr on turn 1</v>
+        <v>Don't let db sheep fool you. OTK swabbie is the true best deck in the game</v>
       </c>
       <c r="B226" t="str">
         <v>One Big Fluke</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Don't let db sheep fool you. OTK swabbie is the true best deck in the game</v>
+        <v>Apotatosaurus is not immune to plant tricks, so doom shroom will destroy it</v>
       </c>
       <c r="B227" t="str">
         <v>One Big Fluke</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Apotatosaurus is not immune to plant tricks, so doom shroom will destroy it</v>
+        <v>Brainana is not a good card. It can almost get cut from hmr...</v>
       </c>
       <c r="B228" t="str">
         <v>One Big Fluke</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Brainana is not a good card. It can almost get cut from hmr...</v>
+        <v>Don't you hate it when you run piles and brick?</v>
       </c>
       <c r="B229" t="str">
         <v>One Big Fluke</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Don't you hate it when you run piles and brick?</v>
+        <v>Getting decks to a 100% winrate by only playing 1 game with them</v>
       </c>
       <c r="B230" t="str">
         <v>One Big Fluke</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Getting decks to a 100% winrate by only playing 1 game with them</v>
+        <v>Using cosmic bean because I saw Vietnamese players running it</v>
       </c>
       <c r="B231" t="str">
         <v>One Big Fluke</v>
@@ -2255,15 +2255,15 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Using cosmic bean because I saw Vietnamese players running it</v>
+        <v>Uploading our 11th revision of Trick-Mech</v>
       </c>
       <c r="B232" t="str">
-        <v>One Big Fluke</v>
+        <v>voof</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Uploading our 11th revision of Trick-Mech</v>
+        <v>I'll be back. (-up dancer)</v>
       </c>
       <c r="B233" t="str">
         <v>voof</v>
@@ -2271,15 +2271,15 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>I'll be back. (-up dancer)</v>
+        <v>Time to add some 5 liners to tbot</v>
       </c>
       <c r="B234" t="str">
-        <v>voof</v>
+        <v>Vortex Dragon</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Time to add some 5 liners to tbot</v>
+        <v>x40 lily pad hackers</v>
       </c>
       <c r="B235" t="str">
         <v>Vortex Dragon</v>
@@ -2287,15 +2287,15 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>x40 lily pad hackers</v>
+        <v>Bricking with final missions</v>
       </c>
       <c r="B236" t="str">
-        <v>Vortex Dragon</v>
+        <v>Xera</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Bricking with final missions</v>
+        <v>Force Field + Soul Patch is an autowin (clueless)</v>
       </c>
       <c r="B237" t="str">
         <v>Xera</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Force Field + Soul Patch is an autowin (clueless)</v>
+        <v>Adding japanese characters to my deck name for +20% draw luck</v>
       </c>
       <c r="B238" t="str">
         <v>Xera</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Adding japanese characters to my deck name for +20% draw luck</v>
+        <v>Enjoying 1/3 Trica (clueless)</v>
       </c>
       <c r="B239" t="str">
         <v>Xera</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Enjoying 1/3 Trica (clueless)</v>
+        <v>Attempting rank 1-50 Sow the Seeds speedrun</v>
       </c>
       <c r="B240" t="str">
         <v>Xera</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Attempting rank 1-50 Sow the Seeds speedrun</v>
+        <v>Being clueless about lane placement</v>
       </c>
       <c r="B241" t="str">
         <v>Xera</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Being clueless about lane placement</v>
+        <v>Nibble on Potato Mines doesn't softlock if there is no zombie in front of them.</v>
       </c>
       <c r="B242" t="str">
         <v>Xera</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Nibble on Potato Mines doesn't softlock if there is no zombie in front of them.</v>
+        <v>Studying PvZH source code in order to figure out why nibble softlocks the game.</v>
       </c>
       <c r="B243" t="str">
         <v>Xera</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Studying PvZH source code in order to figure out why nibble softlocks the game.</v>
+        <v>Most probably a bot with good decks.</v>
       </c>
       <c r="B244" t="str">
         <v>Xera</v>
@@ -2359,71 +2359,71 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Most probably a bot with good decks.</v>
+        <v>Watching the CC's Fig turn into a Starfruit</v>
       </c>
       <c r="B245" t="str">
-        <v>Xera</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Watching the CC's Fig turn into a Starfruit</v>
+        <v>Eating a Tbone steak</v>
       </c>
       <c r="B246" t="str">
-        <v>depressedmonke</v>
+        <v>waltuh</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Eating a Tbone steak</v>
+        <v>i swear these decks are good it's just bad matchups</v>
       </c>
       <c r="B247" t="str">
-        <v>waltuh</v>
+        <v>stingray201</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>i swear these decks are good it's just bad matchups</v>
+        <v>[comp deck] is bad, actually</v>
       </c>
       <c r="B248" t="str">
-        <v>stingray201</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>[comp deck] is bad, actually</v>
+        <v>they'll never expect the fifth gravebuster that I conjured</v>
       </c>
       <c r="B249" t="str">
-        <v>depressedmonke</v>
+        <v>stingray201</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>they'll never expect the fifth gravebuster that I conjured</v>
+        <v>Couldn't Lock the Bathroom :(</v>
       </c>
       <c r="B250" t="str">
-        <v>stingray201</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Couldn't Lock the Bathroom :(</v>
+        <v>Dooming an empty field for card draw</v>
       </c>
       <c r="B251" t="str">
-        <v>depressedmonke</v>
+        <v>Slewer</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Dooming an empty field for card draw</v>
+        <v>Have a nice da</v>
       </c>
       <c r="B252" t="str">
-        <v>Slewer</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Have a nice da</v>
+        <v>Still playing Conman t1 Swashbuckler t2</v>
       </c>
       <c r="B253" t="str">
         <v>depressedmonke</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Still playing Conman t1 Swashbuckler t2</v>
+        <v>Spamming Hearty Treats on Exploding Imps</v>
       </c>
       <c r="B254" t="str">
         <v>depressedmonke</v>
@@ -2439,159 +2439,159 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Spamming Hearty Treats on Exploding Imps</v>
+        <v>Everytime they play a potato mine the nibble in my hand speaks to me</v>
       </c>
       <c r="B255" t="str">
-        <v>depressedmonke</v>
+        <v>hayria</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Everytime they play a potato mine the nibble in my hand speaks to me</v>
+        <v>Making card concepts for Magnet-Shroom that do things with Armored</v>
       </c>
       <c r="B256" t="str">
-        <v>hayria</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Making card concepts for Magnet-Shroom that do things with Armored</v>
+        <v>🐴</v>
       </c>
       <c r="B257" t="str">
-        <v>depressedmonke</v>
+        <v>Seasons</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>🐴</v>
+        <v>projecting my insecurities through tbot status submissions</v>
       </c>
       <c r="B258" t="str">
-        <v>Seasons</v>
+        <v>stingray201</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>projecting my insecurities through tbot status submissions</v>
+        <v>Hate is lame. Spread the love G</v>
       </c>
       <c r="B259" t="str">
-        <v>stingray201</v>
+        <v>Huyn</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Hate is lame. Spread the love G</v>
+        <v>make sure to thank tbot when you ask for decks :)</v>
       </c>
       <c r="B260" t="str">
-        <v>Huyn</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>make sure to thank tbot when you ask for decks :)</v>
+        <v>The nibble in my hand talks to me when my opponent plays a ppm</v>
       </c>
       <c r="B261" t="str">
-        <v>depressedmonke</v>
+        <v>hayriana</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>The nibble in my hand talks to me when my opponent plays a ppm</v>
+        <v>We (yes WE) are all running Typical Beanstalk in 2025</v>
       </c>
       <c r="B262" t="str">
-        <v>hayriana</v>
+        <v>Axol</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>We (yes WE) are all running Typical Beanstalk in 2025</v>
+        <v>If you win a lot of games, are you skilled or just lucky?</v>
       </c>
       <c r="B263" t="str">
-        <v>Axol</v>
+        <v>Alan</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>If you win a lot of games, are you skilled or just lucky?</v>
+        <v>Zombot Stomp in the pocket</v>
       </c>
       <c r="B264" t="str">
-        <v>Alan</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Zombot Stomp in the pocket</v>
+        <v>Real good players win with their favourites</v>
       </c>
       <c r="B265" t="str">
-        <v>depressedmonke</v>
+        <v>meowmeow</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Real good players win with their favourites</v>
+        <v>Submitting conjure slop to tbot after winning 1 game on ladder</v>
       </c>
       <c r="B266" t="str">
-        <v>meowmeow</v>
+        <v>stingray201</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Submitting conjure slop to tbot after winning 1 game on ladder</v>
+        <v>Upvoting my own suggestion</v>
       </c>
       <c r="B267" t="str">
-        <v>stingray201</v>
+        <v>Seasons</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Upvoting my own suggestion</v>
+        <v>The first rule of Fig Club is you don't talk about Fig Club</v>
       </c>
       <c r="B268" t="str">
-        <v>Seasons</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>The first rule of Fig Club is you don't talk about Fig Club</v>
+        <v>2025 is the year of the Snake Grass!</v>
       </c>
       <c r="B269" t="str">
-        <v>depressedmonke</v>
+        <v>Hyshew</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>2025 is the year of the Snake Grass!</v>
+        <v>Letting the opponent ramp to a turn 4 DMD so I can screenshot it and whine about it on reddit</v>
       </c>
       <c r="B270" t="str">
-        <v>Hyshew</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Letting the opponent ramp to a turn 4 DMD so I can screenshot it and whine about it on reddit</v>
+        <v>Who you gonna call... Blockbusters</v>
       </c>
       <c r="B271" t="str">
-        <v>depressedmonke</v>
+        <v>Tbone</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Who you gonna call... Blockbusters</v>
+        <v>When onion rings I pick up the call</v>
       </c>
       <c r="B272" t="str">
-        <v>Tbone</v>
+        <v>Axol</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>When onion rings I pick up the call</v>
+        <v>Getting MUG from a one minion BMR</v>
       </c>
       <c r="B273" t="str">
-        <v>Axol</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Getting MUG from a one minion BMR</v>
+        <v>Doing one push-up every time I see t2 Cryo-Brain</v>
       </c>
       <c r="B274" t="str">
         <v>depressedmonke</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Doing one push-up every time I see t2 Cryo-Brain</v>
+        <v>you are very sleepy give tbone money so he can keep tbot up</v>
       </c>
       <c r="B275" t="str">
         <v>depressedmonke</v>
@@ -2607,31 +2607,31 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>you are very sleepy give tbone money so he can keep tbot up</v>
+        <v>Tbone: officially unc status</v>
       </c>
       <c r="B276" t="str">
-        <v>depressedmonke</v>
+        <v>Rip</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Tbone: officially unc status</v>
+        <v>Getting Pineclone from a Brainana+Dragon Cornucopia</v>
       </c>
       <c r="B277" t="str">
-        <v>Rip</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Getting Pineclone from a Brainana+Dragon Cornucopia</v>
+        <v>Ifdeckass: /SuggestAsMemeDeck</v>
       </c>
       <c r="B278" t="str">
-        <v>depressedmonke</v>
+        <v>Seasons</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Ifdeckass: /SuggestAsMemeDeck</v>
+        <v>ifdeckgood: /SuggestAsLadderDeck</v>
       </c>
       <c r="B279" t="str">
         <v>Seasons</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>ifdeckgood: /SuggestAsLadderDeck</v>
+        <v>ifdeckbad: /SuggestAsCompetitiveDeck</v>
       </c>
       <c r="B280" t="str">
         <v>Seasons</v>
@@ -2647,79 +2647,79 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ifdeckbad: /SuggestAsCompetitiveDeck</v>
+        <v>Going Nuts with Go-Nuts</v>
       </c>
       <c r="B281" t="str">
-        <v>Seasons</v>
+        <v>depressedmonke</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Going Nuts with Go-Nuts</v>
+        <v>Attempting to softlock irl by biting a cactus</v>
       </c>
       <c r="B282" t="str">
-        <v>depressedmonke</v>
+        <v>depressedmonke_</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Attempting to softlock irl by biting a cactus</v>
+        <v>Mono gang</v>
       </c>
       <c r="B283" t="str">
-        <v>depressedmonke_</v>
+        <v>waltuh</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Mono gang</v>
+        <v>Playing Celestial Custodian in Graveyard to correct its turn order</v>
       </c>
       <c r="B284" t="str">
-        <v>waltuh</v>
+        <v>depressedmonke_</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Playing Celestial Custodian in Graveyard to correct its turn order</v>
+        <v>Ten likes and Huyn draws Swabbie with huge muscles and abs</v>
       </c>
       <c r="B285" t="str">
-        <v>depressedmonke_</v>
+        <v>lumpymilktea</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Ten likes and Huyn draws Swabbie with huge muscles and abs</v>
+        <v>Taking deckbuilding lessons from Crimpton 🛹</v>
       </c>
       <c r="B286" t="str">
-        <v>lumpymilktea</v>
+        <v>depressedmonke_</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Taking deckbuilding lessons from Crimpton 🛹</v>
+        <v>Ferb, I know what we're gonna do today!</v>
       </c>
       <c r="B287" t="str">
-        <v>depressedmonke_</v>
+        <v>Tbone</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Ferb, I know what we're gonna do today!</v>
+        <v>Spinning the wheel for which widely-considered-mediocre card is now busted because of a certain tech</v>
       </c>
       <c r="B288" t="str">
-        <v>Tbone</v>
+        <v>stingray</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Spinning the wheel for which widely-considered-mediocre card is now busted because of a certain tech</v>
+        <v>Getting mass downvoted after explaining why ANB isn't S tier</v>
       </c>
       <c r="B289" t="str">
-        <v>stingray</v>
+        <v>4-Pound Plate of Pasta</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Getting mass downvoted after explaining why ANB isn't S tier</v>
+        <v>Gee i sure hope I don't miss this eyespore fusion</v>
       </c>
       <c r="B290" t="str">
         <v>4-Pound Plate of Pasta</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Gee i sure hope I don't miss this eyespore fusion</v>
+        <v>Reading the 400th crippling DMD nerf on the sub</v>
       </c>
       <c r="B291" t="str">
         <v>4-Pound Plate of Pasta</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Reading the 400th crippling DMD nerf on the sub</v>
+        <v>Roping my opponent so I can listen to the low health theme</v>
       </c>
       <c r="B292" t="str">
         <v>4-Pound Plate of Pasta</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Roping my opponent so I can listen to the low health theme</v>
+        <v>Running Buff-Shroom in Cycle-Cap to counter ZM Sig</v>
       </c>
       <c r="B293" t="str">
         <v>4-Pound Plate of Pasta</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Running Buff-Shroom in Cycle-Cap to counter ZM Sig</v>
+        <v>Getting a Magic Beanstalk from the 15 daily streak reward</v>
       </c>
       <c r="B294" t="str">
         <v>4-Pound Plate of Pasta</v>
@@ -2759,23 +2759,23 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Getting a Magic Beanstalk from the 15 daily streak reward</v>
+        <v>getting nothing because it's not worth logging in</v>
       </c>
       <c r="B295" t="str">
-        <v>4-Pound Plate of Pasta</v>
+        <v>Stingray</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>getting nothing because it's not worth logging in</v>
+        <v>Using Eyespore as an aggro card</v>
       </c>
       <c r="B296" t="str">
-        <v>Stingray</v>
+        <v>Durga</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Using Eyespore as an aggro card</v>
+        <v>Ign: 40anb swr</v>
       </c>
       <c r="B297" t="str">
         <v>Durga</v>
@@ -2783,95 +2783,95 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Ign: 40anb swr</v>
+        <v>Sunshroom is destroying the meta, nerf Miner</v>
       </c>
       <c r="B298" t="str">
-        <v>Durga</v>
+        <v>FrozenFighter</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Sunshroom is destroying the meta, nerf Miner</v>
+        <v>With Reincarnation, VRH and Fig, we could be able to get a Reliable Molekale..... stares at camera</v>
       </c>
       <c r="B299" t="str">
-        <v>FrozenFighter</v>
+        <v>StingRay</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>With Reincarnation, VRH and Fig, we could be able to get a Reliable Molekale..... stares at camera</v>
+        <v>When your Molekale spawns a Pineclone</v>
       </c>
       <c r="B300" t="str">
-        <v>StingRay</v>
+        <v>Frozen Fighter</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>When your Molekale spawns a Pineclone</v>
+        <v>turn 1 black hole turn 2 double cheese</v>
       </c>
       <c r="B301" t="str">
-        <v>Frozen Fighter</v>
+        <v>Huyn</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>turn 1 black hole turn 2 double cheese</v>
+        <v>rose is so OP why won't my 4x5 HG conjure pile work on her???</v>
       </c>
       <c r="B302" t="str">
-        <v>Huyn</v>
+        <v>StingRay</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>rose is so OP why won't my 4x5 HG conjure pile work on her???</v>
+        <v>Fighting for Corndog</v>
       </c>
       <c r="B303" t="str">
-        <v>StingRay</v>
+        <v>Waltuh</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Fighting for Corndog</v>
+        <v>Which hero can play OTK Cryo Yeti? HG? No. BF? No. GS? Yes.</v>
       </c>
       <c r="B304" t="str">
-        <v>Waltuh</v>
+        <v>connorthepeach</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Which hero can play OTK Cryo Yeti? HG? No. BF? No. GS? Yes.</v>
+        <v>Helping Vengeful Cyborg look for his lost toupee</v>
       </c>
       <c r="B305" t="str">
-        <v>connorthepeach</v>
+        <v>Pasta</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Helping Vengeful Cyborg look for his lost toupee</v>
+        <v>the duo: pineclone from cornucopia and mug from bmr</v>
       </c>
       <c r="B306" t="str">
-        <v>Pasta</v>
+        <v>IGN: FrozenOwO</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>the duo: pineclone from cornucopia and mug from bmr</v>
+        <v>Tbot: Sponsored by Pop Smarts, The Brain Flavored Treat</v>
       </c>
       <c r="B307" t="str">
-        <v>IGN: FrozenOwO</v>
+        <v>KingFish</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Tbot: Sponsored by Pop Smarts, The Brain Flavored Treat</v>
+        <v>captain cucumber xpol is like teacher tcap</v>
       </c>
       <c r="B308" t="str">
-        <v>KingFish</v>
+        <v>IGN: FrozenOwO</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>captain cucumber xpol is like teacher tcap</v>
+        <v>t1 puff shroom blazing bark vs the nefarious t1 cut down to size</v>
       </c>
       <c r="B309" t="str">
         <v>IGN: FrozenOwO</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>t1 puff shroom blazing bark vs the nefarious t1 cut down to size</v>
+        <v>deja vu, i conjured 2 xpol from my xpol</v>
       </c>
       <c r="B310" t="str">
         <v>IGN: FrozenOwO</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>deja vu, i conjured 2 xpol from my xpol</v>
+        <v>smash players betting their life savings on drawing t1 black hole</v>
       </c>
       <c r="B311" t="str">
         <v>IGN: FrozenOwO</v>
@@ -2895,39 +2895,39 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>smash players betting their life savings on drawing t1 black hole</v>
+        <v>responding to wild berry with cryobrain</v>
       </c>
       <c r="B312" t="str">
-        <v>IGN: FrozenOwO</v>
+        <v>Druudey</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>responding to wild berry with cryobrain</v>
+        <v>Every time you ignore this message a seedling dies</v>
       </c>
       <c r="B313" t="str">
-        <v>Druudey</v>
+        <v>Hyshew</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Every time you ignore this message a seedling dies</v>
+        <v>Though zombies can't get ill, this plague is totally sick</v>
       </c>
       <c r="B314" t="str">
-        <v>Hyshew</v>
+        <v>Axol</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Though zombies can't get ill, this plague is totally sick</v>
+        <v>if you think about it, black eyed pea in coffee grounds is basically a zombie whenever going viral is played</v>
       </c>
       <c r="B315" t="str">
-        <v>Axol</v>
+        <v>IGN: FrozenOwO</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>if you think about it, black eyed pea in coffee grounds is basically a zombie whenever going viral is played</v>
+        <v>t1 waxer is basically t1 cheesecutter of the brainy class</v>
       </c>
       <c r="B316" t="str">
         <v>IGN: FrozenOwO</v>
@@ -2935,87 +2935,87 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>t1 waxer is basically t1 cheesecutter of the brainy class</v>
+        <v>Lying to new players about new balance patches</v>
       </c>
       <c r="B317" t="str">
-        <v>IGN: FrozenOwO</v>
+        <v>Axol</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Lying to new players about new balance patches</v>
+        <v>Playing Plant Food on Imitater so it doesn't trigger Mime Garg's ability</v>
       </c>
       <c r="B318" t="str">
-        <v>Axol</v>
+        <v>4-Pound Plate of Pasta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Playing Plant Food on Imitater so it doesn't trigger Mime Garg's ability</v>
+        <v>slungus</v>
       </c>
       <c r="B319" t="str">
-        <v>4-Pound Plate of Pasta</v>
+        <v>catconnor</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>slungus</v>
+        <v>vibe coding the nibble softlocks</v>
       </c>
       <c r="B320" t="str">
-        <v>catconnor</v>
+        <v>IGN: FrozenOwO</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>vibe coding the nibble softlocks</v>
+        <v>Evolving Gatling on Three-Nut</v>
       </c>
       <c r="B321" t="str">
-        <v>IGN: FrozenOwO</v>
+        <v>4lbpsta</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Evolving Gatling on Three-Nut</v>
+        <v>Gravitrees hate you</v>
       </c>
       <c r="B322" t="str">
-        <v>4lbpsta</v>
+        <v>legodarthglobox</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Gravitrees hate you</v>
+        <v>Quit PvZh ❌ -&gt; relapse ✅ 🦆</v>
       </c>
       <c r="B323" t="str">
-        <v>legodarthglobox</v>
+        <v>7oshay</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quit PvZh ❌ -&gt; relapse ✅ 🦆</v>
+        <v>terrifying a Lily of the Valley to heights</v>
       </c>
       <c r="B324" t="str">
-        <v>7oshay</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>terrifying a Lily of the Valley to heights</v>
+        <v>if you want your takes validated just have a seasoned comp player say them</v>
       </c>
       <c r="B325" t="str">
-        <v>fx78945</v>
+        <v>stingray201_</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>if you want your takes validated just have a seasoned comp player say them</v>
+        <v>cyborg is a corndog that gives back a smoosh-shroom</v>
       </c>
       <c r="B326" t="str">
-        <v>stingray201_</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>cyborg is a corndog that gives back a smoosh-shroom</v>
+        <v>Using pecanolith to tech pb! one waxer later:</v>
       </c>
       <c r="B327" t="str">
         <v>fx78945</v>
@@ -3023,23 +3023,23 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Using pecanolith to tech pb! one waxer later:</v>
+        <v>busy not playing the game</v>
       </c>
       <c r="B328" t="str">
-        <v>fx78945</v>
+        <v>aveorni</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>busy not playing the game</v>
+        <v>Every pvzh deck is midrange if you stop overthinking</v>
       </c>
       <c r="B329" t="str">
-        <v>aveorni</v>
+        <v>slungusnor</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Every pvzh deck is midrange if you stop overthinking</v>
+        <v>Buying the armored pack</v>
       </c>
       <c r="B330" t="str">
         <v>slungusnor</v>
@@ -3047,114 +3047,114 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Buying the armored pack</v>
+        <v>playing one-liner decks on ranked -wait</v>
       </c>
       <c r="B331" t="str">
-        <v>slungusnor</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>playing one-liner decks on ranked -wait</v>
+        <v>I don't give the haters mushroom, cause I know I'm a fun guy</v>
       </c>
       <c r="B332" t="str">
-        <v>fx78945</v>
+        <v>axolhitori</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>I don't give the haters mushroom, cause I know I'm a fun guy</v>
+        <v>zombot is good anywhere, except when you run it</v>
       </c>
       <c r="B333" t="str">
-        <v>axolhitori</v>
+        <v>sasebest</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>zombot is good anywhere, except when you run it</v>
+        <v>Attempting to use GS sig on an Untrickable Zombie</v>
       </c>
       <c r="B334" t="str">
-        <v>sasebest</v>
+        <v>4lbpsta</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Attempting to use GS sig on an Untrickable Zombie</v>
+        <v>using Yeti's infinite lunchboxes to solve world hunger</v>
       </c>
       <c r="B335" t="str">
-        <v>4lbpsta</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>using Yeti's infinite lunchboxes to solve world hunger</v>
+        <v>Settle it in PvZHeroes</v>
       </c>
       <c r="B336" t="str">
-        <v>fx78945</v>
+        <v>legodarthglobox</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Settle it in PvZHeroes</v>
+        <v>playing doomshroom to draw a card for my dinos- wait where are they?</v>
       </c>
       <c r="B337" t="str">
-        <v>legodarthglobox</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>playing doomshroom to draw a card for my dinos- wait where are they?</v>
+        <v>john7127 is the best player</v>
       </c>
       <c r="B338" t="str">
-        <v>fx78945</v>
+        <v>slungusnor</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>john7127 is the best player</v>
+        <v>Trying to evolve cob cannon on a team-up but accidentally putting cob in front of it</v>
       </c>
       <c r="B339" t="str">
-        <v>slungusnor</v>
+        <v>ddp0745</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Trying to evolve cob cannon on a team-up but accidentally putting cob in front of it</v>
+        <v>playing my cattail on a lilypad</v>
       </c>
       <c r="B340" t="str">
-        <v>ddp0745</v>
+        <v>fx78945</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>playing my cattail on a lilypad</v>
+        <v>Playing Flag + double Genex into Scorch</v>
       </c>
       <c r="B341" t="str">
-        <v>fx78945</v>
+        <v>4lbpsta</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Playing Flag + double Genex into Scorch</v>
+        <v>Mulling my Pepper in exchange for Lil' Buddy</v>
       </c>
       <c r="B342" t="str">
-        <v>4lbpsta</v>
+        <v>binaclepinnacle</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Mulling my Pepper in exchange for Lil' Buddy</v>
+        <v>Naming my decks after Strategy Decks to confuse people</v>
       </c>
       <c r="B343" t="str">
-        <v>binaclepinnacle</v>
+        <v>4lbpsta</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Naming my decks after Strategy Decks to confuse people</v>
+        <v>Fixing bugs by adding new ones</v>
       </c>
       <c r="B344" t="str">
-        <v>4lbpsta</v>
+        <v>Maker</v>
       </c>
     </row>
   </sheetData>
